--- a/Fruto - Pipeline - Mat. Fieldspec/analise_completa_resultados_cv.xlsx
+++ b/Fruto - Pipeline - Mat. Fieldspec/analise_completa_resultados_cv.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.7572126388549805</v>
+        <v>0.7823598384857178</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3.086739301681519</v>
+        <v>3.19235634803772</v>
       </c>
     </row>
     <row r="4">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8263306617736816</v>
+        <v>0.8501005172729492</v>
       </c>
     </row>
     <row r="5">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.035609722137451</v>
+        <v>0.9310710430145264</v>
       </c>
     </row>
     <row r="6">
@@ -656,38 +656,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7457630534040113</v>
+        <v>0.7478465034687443</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1028631613899992</v>
+        <v>0.1125639080575354</v>
       </c>
       <c r="G6" t="n">
-        <v>19.86620121482039</v>
+        <v>19.76628957710632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7457630534040113</v>
+        <v>0.7478465034687443</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'model__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.7612006664276123</v>
+        <v>31.80070376396179</v>
       </c>
     </row>
     <row r="7">
@@ -703,7 +703,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7386295499349365</v>
+        <v>0.7457630534040113</v>
       </c>
       <c r="F7" t="n">
-        <v>0.109678494132419</v>
+        <v>0.1028631613899992</v>
       </c>
       <c r="G7" t="n">
-        <v>20.2517108537734</v>
+        <v>19.86620121482039</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7386295499349365</v>
+        <v>0.7457630534040113</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.7264015674591064</v>
+        <v>0.8007128238677979</v>
       </c>
     </row>
     <row r="8">
@@ -745,25 +745,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7368687252646114</v>
+        <v>0.7386295499349365</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1373264332021021</v>
+        <v>0.109678494132419</v>
       </c>
       <c r="G8" t="n">
-        <v>20.09583459962839</v>
+        <v>20.2517108537734</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7368687252646114</v>
+        <v>0.7386295499349365</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.003277063369751</v>
+        <v>0.7706506252288818</v>
       </c>
     </row>
     <row r="9">
@@ -787,25 +787,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7364043449249282</v>
+        <v>0.7368687252646114</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1010119196459963</v>
+        <v>0.1373264332021021</v>
       </c>
       <c r="G9" t="n">
-        <v>20.32701257358256</v>
+        <v>20.09583459962839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7364043449249282</v>
+        <v>0.7368687252646114</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.7836034297943115</v>
+        <v>0.9007284641265869</v>
       </c>
     </row>
     <row r="10">
@@ -829,25 +829,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7303446435200619</v>
+        <v>0.7364043449249282</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1099794639412245</v>
+        <v>0.1010119196459963</v>
       </c>
       <c r="G10" t="n">
-        <v>20.57323328734136</v>
+        <v>20.32701257358256</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7303446435200619</v>
+        <v>0.7364043449249282</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1.013639688491821</v>
+        <v>0.8073406219482422</v>
       </c>
     </row>
     <row r="11">
@@ -871,25 +871,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.697466018734753</v>
+        <v>0.7303446435200619</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1237600246273632</v>
+        <v>0.1099794639412245</v>
       </c>
       <c r="G11" t="n">
-        <v>21.58468572992863</v>
+        <v>20.57323328734136</v>
       </c>
       <c r="H11" t="n">
-        <v>0.697466018734753</v>
+        <v>0.7303446435200619</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.7707822322845459</v>
+        <v>0.9821138381958008</v>
       </c>
     </row>
     <row r="12">
@@ -908,38 +908,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6651657853530362</v>
+        <v>0.728167799283449</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1232845632548366</v>
+        <v>0.1651670573773028</v>
       </c>
       <c r="G12" t="n">
-        <v>22.66066315551609</v>
+        <v>20.37099227741776</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6651657853530362</v>
+        <v>0.728167799283449</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'model__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.821340799331665</v>
+        <v>33.75856637954712</v>
       </c>
     </row>
     <row r="13">
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -964,24 +964,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6651657853524662</v>
+        <v>0.7281259093615561</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1232845632559793</v>
+        <v>0.1370875636762304</v>
       </c>
       <c r="G13" t="n">
-        <v>22.66066315552809</v>
+        <v>20.56100370627633</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6651657853524662</v>
+        <v>0.7281259093615561</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'model__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.7874181270599365</v>
+        <v>13.53354048728943</v>
       </c>
     </row>
     <row r="14">
@@ -997,25 +997,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6036423329711003</v>
+        <v>0.697466018734753</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1498256768363453</v>
+        <v>0.1237600246273632</v>
       </c>
       <c r="G14" t="n">
-        <v>24.46927219043578</v>
+        <v>21.58468572992863</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6036423329711003</v>
+        <v>0.697466018734753</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1.104975700378418</v>
+        <v>0.7907423973083496</v>
       </c>
     </row>
     <row r="15">
@@ -1034,38 +1034,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5959608349175307</v>
+        <v>0.6973723425515732</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1462620413330654</v>
+        <v>0.137855714314989</v>
       </c>
       <c r="G15" t="n">
-        <v>24.82442148042011</v>
+        <v>21.479607619426</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5959608349175307</v>
+        <v>0.6973723425515732</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'model__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1.008376121520996</v>
+        <v>11.01331806182861</v>
       </c>
     </row>
     <row r="16">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1090,24 +1090,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5837852886301912</v>
+        <v>0.6973723425515732</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1568649304885326</v>
+        <v>0.137855714314989</v>
       </c>
       <c r="G16" t="n">
-        <v>25.14803606312541</v>
+        <v>21.479607619426</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5837852886301912</v>
+        <v>0.6973723425515732</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'model__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1.113326787948608</v>
+        <v>9.05549144744873</v>
       </c>
     </row>
     <row r="17">
@@ -1118,38 +1118,1382 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Wavelet_Denoising</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6958863089898952</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1386915547435018</v>
+      </c>
+      <c r="G17" t="n">
+        <v>21.52922506527224</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6958863089898952</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>33.68459248542786</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Continuum_Removal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.694243977289968</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1275447309478703</v>
+      </c>
+      <c r="G18" t="n">
+        <v>21.51563288982706</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.694243977289968</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>14.51191473007202</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OSC_1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6889852301754947</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1672567591931507</v>
+      </c>
+      <c r="G19" t="n">
+        <v>21.70919920853868</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6889852301754947</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1.09980320930481</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6880187616693975</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.172677369819595</v>
+      </c>
+      <c r="G20" t="n">
+        <v>21.62263816685554</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.6880187616693975</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1.164463043212891</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Wavelet_Denoising</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6879594953382855</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1727171394985512</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21.62349623007927</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6879594953382855</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1.705979108810425</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SNV_Detrend_SG_D1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.6879265919522645</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1727391581527574</v>
+      </c>
+      <c r="G22" t="n">
+        <v>21.62442040960672</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6879265919522645</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9175100326538086</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OSC_2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6855241378580732</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1591946065375377</v>
+      </c>
+      <c r="G23" t="n">
+        <v>21.75116626958749</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6855241378580732</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 10}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1.366376161575317</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Normalize</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.684466354359111</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1524274192247903</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22.1973256607024</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.684466354359111</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 20}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8517751693725586</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Continuum_Removal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6806016519707805</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1392918120137803</v>
+      </c>
+      <c r="G25" t="n">
+        <v>21.91477721839029</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6806016519707805</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>673.1493184566498</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6673577566559264</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1496948776279058</v>
+      </c>
+      <c r="G26" t="n">
+        <v>22.69261289659733</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6673577566559264</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 20}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1.210952997207642</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMSC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6671571312157817</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.1500437371581927</v>
+      </c>
+      <c r="G27" t="n">
+        <v>22.69832547933093</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6671571312157817</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 20}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9240272045135498</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Detrend</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6661556861077281</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1460476772991672</v>
+      </c>
+      <c r="G28" t="n">
+        <v>22.63409427470306</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6661556861077281</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 20}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.829575777053833</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>PLSR</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMSC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6651657853530362</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.1232845632548366</v>
+      </c>
+      <c r="G29" t="n">
+        <v>22.66066315551609</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6651657853530362</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'model__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8617172241210938</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PLSR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6651657853524662</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1232845632559793</v>
+      </c>
+      <c r="G30" t="n">
+        <v>22.66066315552809</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6651657853524662</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'model__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9058530330657959</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Detrend</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6540828225698835</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1504341469303058</v>
+      </c>
+      <c r="G31" t="n">
+        <v>23.06988627347214</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6540828225698835</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>9.74915337562561</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SNV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6394590994162253</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1680775746488588</v>
+      </c>
+      <c r="G32" t="n">
+        <v>23.55274736458711</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6394590994162253</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 20}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9955611228942871</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SG_D2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6358613338282281</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1267717382259375</v>
+      </c>
+      <c r="G33" t="n">
+        <v>24.12568093856609</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6358613338282281</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>12.95129251480103</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6358312643804287</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.1416126067934894</v>
+      </c>
+      <c r="G34" t="n">
+        <v>23.78655515408832</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6358312643804287</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>21.73987221717834</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMSC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6358312643787081</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1416126067970581</v>
+      </c>
+      <c r="G35" t="n">
+        <v>23.78655515411336</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6358312643787081</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>12.9947190284729</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>OPLS2_SNV_SG_D1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6287414899095066</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2913311281053384</v>
+      </c>
+      <c r="G36" t="n">
+        <v>23.28620456291402</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6287414899095066</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>26.35242486000061</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Normalize</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6265158805905043</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1293311821487664</v>
+      </c>
+      <c r="G37" t="n">
+        <v>24.14174466426777</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6265158805905043</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>11.08403491973877</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PLSR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>OPLS2_SNV_SG_D1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6036423329711003</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1498256768363453</v>
+      </c>
+      <c r="G38" t="n">
+        <v>24.46927219043578</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6036423329711003</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'model__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1.075331926345825</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PLSR</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OPLS1_SNV_SG_D1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5959608349175307</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1462620413330654</v>
+      </c>
+      <c r="G39" t="n">
+        <v>24.82442148042011</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5959608349175307</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'model__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.9927043914794922</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PLSR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MSC_SG_OSC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5837852886301912</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.1568649304885326</v>
+      </c>
+      <c r="G40" t="n">
+        <v>25.14803606312541</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5837852886301912</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'model__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1.058034658432007</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PLSR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Continuum_Removal</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>independente</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
         <v>0.5748789560632097</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F41" t="n">
         <v>0.2017623926686886</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G41" t="n">
         <v>25.36215481161548</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H41" t="n">
         <v>0.5748789560632097</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>{'model__n_components': 15}</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>5.773141384124756</v>
+      <c r="J41" t="n">
+        <v>6.053139448165894</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SG_D1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.563694040745136</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2039898396485982</v>
+      </c>
+      <c r="G42" t="n">
+        <v>25.94996474209019</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.563694040745136</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>11.84759950637817</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SG_D1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5536111481071961</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.178102674506109</v>
+      </c>
+      <c r="G43" t="n">
+        <v>25.9663533700771</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5536111481071961</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 20}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8917131423950195</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OPLS1_SNV_SG_D1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.5432334691327971</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.2008266314638987</v>
+      </c>
+      <c r="G44" t="n">
+        <v>26.5266794389507</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.5432334691327971</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.360605239868164</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MSC_SG_OSC</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5375304511956627</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2052857852274378</v>
+      </c>
+      <c r="G45" t="n">
+        <v>26.66620779170324</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5375304511956627</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 15}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.593544721603394</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OPLS1_SNV_SG_D1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.5365745211609859</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.3269115030574147</v>
+      </c>
+      <c r="G46" t="n">
+        <v>26.39069463835996</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5365745211609859</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>19.9713180065155</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SVMR</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MSC_SG_OSC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.5227874660368109</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.3433726270748472</v>
+      </c>
+      <c r="G47" t="n">
+        <v>26.72382136057694</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5227874660368109</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>35.7845778465271</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OPLS2_SNV_SG_D1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>dependente</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.4747343703996936</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.2962528675072814</v>
+      </c>
+      <c r="G48" t="n">
+        <v>27.73297083687253</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.4747343703996936</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 20}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.934514045715332</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Firmness (N)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PCR</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SG_D2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>independente</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.3971473668176518</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.2389966276749148</v>
+      </c>
+      <c r="G49" t="n">
+        <v>30.6352049086724</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.3971473668176518</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'model__pca__n_components': 5}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8587298393249512</v>
       </c>
     </row>
   </sheetData>
